--- a/veterinarian_forms/001_veterinarian_appointment_form--veterinarian_forms.xlsx
+++ b/veterinarian_forms/001_veterinarian_appointment_form--veterinarian_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Veterinarian Name</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>appointment_time</t>
+          <t>appointment_time_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Appointment Time</t>
+          <t>Appointment Time 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Veterinarian Confirmation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Appointment Confirmation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Veterinarian Name Confirmation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Clinic Confirmation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Owner Signature Confirmation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Confirm</t>
+          <t>Owner Date Confirmation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
